--- a/Feuille de calcul de la base de connaissance-1.xlsx
+++ b/Feuille de calcul de la base de connaissance-1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Expat-Electronic\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\odc\Downloads\base-connaissance-depanange-main\base-connaissance-depanange-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19310" windowHeight="7040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Entrées base de connaissances" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="82">
   <si>
     <t>Commentaires</t>
   </si>
@@ -163,9 +163,6 @@
     <t>Mise en réseau</t>
   </si>
   <si>
-    <t>Ex. 1</t>
-  </si>
-  <si>
     <t>exemple 2</t>
   </si>
   <si>
@@ -182,9 +179,6 @@
   </si>
   <si>
     <t>Problème d'instance SSH vers EC2</t>
-  </si>
-  <si>
-    <t>Ex. 2</t>
   </si>
   <si>
     <t>exemple 3</t>
@@ -232,9 +226,6 @@
     <t>Notions de base sur l'informatique</t>
   </si>
   <si>
-    <t>Ex. 3</t>
-  </si>
-  <si>
     <t>exemple 4</t>
   </si>
   <si>
@@ -254,9 +245,6 @@
   </si>
   <si>
     <t>Le service Linux a cessé de fonctionner</t>
-  </si>
-  <si>
-    <t>Ex. 4</t>
   </si>
   <si>
     <t>Stockage et gestion des données</t>
@@ -286,12 +274,154 @@
 3. Vérifiez que le port TCP 22 est ouvert au trafic entrant pour le groupe de sécurité associé à l'instance EC2.
 </t>
   </si>
+  <si>
+    <t>LAB:</t>
+  </si>
+  <si>
+    <t>178--Lab - Utilisation d'AWS Lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après la création de l evenement  suite au teste Après quelques instants, la page affiche le message « Résultat de l'exécution: échec ».  </t>
+  </si>
+  <si>
+    <t>Le port 3306 est innaccessible</t>
+  </si>
+  <si>
+    <t>LAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impossible de se connecter à votre instanceImpossible de se connecter à votre instance
+Erreur lors de l'établissement de la connexion SSH à votre instance. Veuillez réessayer plus tard.
+</t>
+  </si>
+  <si>
+    <t>connexion shh échoué</t>
+  </si>
+  <si>
+    <t>impossible de se connecter au port ssh</t>
+  </si>
+  <si>
+    <t>ajouter une règle entrante pour le port ssh dans le groupe de securité</t>
+  </si>
+  <si>
+    <t>N /A</t>
+  </si>
+  <si>
+    <t>171--Lab - Création d'instances Amazon EC2</t>
+  </si>
+  <si>
+    <t>LAB:171</t>
+  </si>
+  <si>
+    <t>un groupe de sécurité autorise les connections vers le serveur et defini qui peut acceder a quoi</t>
+  </si>
+  <si>
+    <t>Le nom du DNS NE marche pas</t>
+  </si>
+  <si>
+    <t>Le protocol httpd est inactif</t>
+  </si>
+  <si>
+    <t>systemctl restarthttpd</t>
+  </si>
+  <si>
+    <t>Ce site est inaccessible
+44.248.147.252 a mis trop de temps à répondre</t>
+  </si>
+  <si>
+    <t>n /A</t>
+  </si>
+  <si>
+    <t>Erreur AWS CLI</t>
+  </si>
+  <si>
+    <t>Unable to locate credentials</t>
+  </si>
+  <si>
+    <t>Pas de credentials AWS</t>
+  </si>
+  <si>
+    <t>Erreur Bash</t>
+  </si>
+  <si>
+    <t>substring expression &lt; 0</t>
+  </si>
+  <si>
+    <t>Variable AZ vide</t>
+  </si>
+  <si>
+    <t>Vérifier metadata EC2</t>
+  </si>
+  <si>
+    <t>Script ne fonctionne pas</t>
+  </si>
+  <si>
+    <t>AMI non récupérée</t>
+  </si>
+  <si>
+    <t>Mauvaise commande ou permissions</t>
+  </si>
+  <si>
+    <t>Corriger syntaxe + vérifier IAM</t>
+  </si>
+  <si>
+    <t>Problème environnement</t>
+  </si>
+  <si>
+    <t>AZ vide</t>
+  </si>
+  <si>
+    <t>Pas sur EC2 ou metadata bloqué</t>
+  </si>
+  <si>
+    <t>Exécuter sur EC2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Configurer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>aws configure</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ou ajouter rôle IAM</t>
+    </r>
+  </si>
+  <si>
+    <t>AWS CLI</t>
+  </si>
+  <si>
+    <t>IAM</t>
+  </si>
+  <si>
+    <t>curl</t>
+  </si>
+  <si>
+    <t>EC2</t>
+  </si>
+  <si>
+    <t>Défi 2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +506,26 @@
       <color theme="1"/>
       <name val="Amazon Ember Light"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -408,7 +558,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -467,15 +617,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -487,17 +628,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,12 +655,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -550,10 +693,10 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -583,26 +726,68 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -942,21 +1127,21 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I186"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="20"/>
+  <dimension ref="A1:I182"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="20.25"/>
   <cols>
-    <col min="1" max="1" width="28.6328125" style="3" customWidth="1"/>
-    <col min="2" max="3" width="32.453125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="81.54296875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="38.453125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="32.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="81.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="38.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="38" style="3" customWidth="1"/>
-    <col min="7" max="7" width="42.453125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="49.6328125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="61.6328125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="11.453125" style="3"/>
+    <col min="7" max="7" width="42.42578125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="49.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="61.5703125" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="12" customFormat="1" ht="65.400000000000006" customHeight="1" thickBot="1">
+    <row r="1" spans="1:9" s="12" customFormat="1" ht="65.45" customHeight="1" thickBot="1">
       <c r="A1" s="9" t="s">
         <v>7</v>
       </c>
@@ -983,17 +1168,15 @@
       </c>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:9" ht="409.25" customHeight="1">
+    <row r="2" spans="1:9" ht="409.35" customHeight="1" thickBot="1">
       <c r="A2" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>15</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B2" s="13"/>
       <c r="C2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="21" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="14" t="s">
@@ -1012,637 +1195,854 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="279.89999999999998" customHeight="1">
-      <c r="A3" s="21" t="s">
-        <v>22</v>
+    <row r="3" spans="1:9" ht="279.95" customHeight="1" thickBot="1">
+      <c r="A3" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="207" customHeight="1" thickBot="1">
+      <c r="A4" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="24" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="207" customHeight="1" thickBot="1">
+      <c r="A5" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="25"/>
+    </row>
+    <row r="6" spans="1:9" ht="209.25" customHeight="1" thickBot="1">
+      <c r="A6" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="23.25" customHeight="1">
+      <c r="A7" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="207" customHeight="1">
-      <c r="A4" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="207" customHeight="1" thickBot="1">
-      <c r="A5" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="22.5">
-      <c r="A6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" ht="22.5">
-      <c r="A7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" ht="22.5">
-      <c r="A8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" ht="22.5">
-      <c r="A9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" ht="22.5">
-      <c r="A10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" ht="22.5">
-      <c r="A11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" ht="22.5">
-      <c r="A12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" ht="22.5">
-      <c r="A13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" ht="22.5">
-      <c r="A14" s="5"/>
-    </row>
-    <row r="15" spans="1:9" ht="22.5">
-      <c r="A15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" ht="22.5">
-      <c r="A16" s="5"/>
-    </row>
-    <row r="17" spans="1:1" ht="22.5">
-      <c r="A17" s="5"/>
-    </row>
-    <row r="18" spans="1:1" ht="22.5">
-      <c r="A18" s="5"/>
-    </row>
-    <row r="19" spans="1:1" ht="22.5">
-      <c r="A19" s="5"/>
-    </row>
-    <row r="20" spans="1:1" ht="22.5">
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+    </row>
+    <row r="8" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A8" s="34"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+    </row>
+    <row r="9" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A9" s="34"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+    </row>
+    <row r="10" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A10" s="34"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+    </row>
+    <row r="11" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A11" s="34"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+    </row>
+    <row r="12" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A12" s="34"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+    </row>
+    <row r="13" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A13" s="34"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+    </row>
+    <row r="14" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A14" s="34"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+    </row>
+    <row r="15" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="27"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="29"/>
+      <c r="B17" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+    </row>
+    <row r="18" spans="1:8" ht="23.25" customHeight="1">
+      <c r="A18" s="29"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+    </row>
+    <row r="19" spans="1:8" ht="23.25" customHeight="1">
+      <c r="A19" s="29"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+    </row>
+    <row r="20" spans="1:8" ht="23.25">
       <c r="A20" s="5"/>
-    </row>
-    <row r="21" spans="1:1" ht="22.5">
-      <c r="A21" s="5"/>
-    </row>
-    <row r="22" spans="1:1" ht="22.5">
-      <c r="A22" s="5"/>
-    </row>
-    <row r="23" spans="1:1" ht="22.5">
-      <c r="A23" s="5"/>
-    </row>
-    <row r="24" spans="1:1" ht="22.5">
-      <c r="A24" s="5"/>
-    </row>
-    <row r="25" spans="1:1" ht="22.5">
+      <c r="B20" s="27"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+    </row>
+    <row r="21" spans="1:8" ht="40.5" customHeight="1">
+      <c r="A21" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="40.5" customHeight="1">
+      <c r="A22" s="29"/>
+      <c r="C22" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="40.5" customHeight="1">
+      <c r="A23" s="29"/>
+      <c r="C23" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="40.5" customHeight="1">
+      <c r="A24" s="29"/>
+      <c r="C24" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="23.25">
       <c r="A25" s="5"/>
-    </row>
-    <row r="26" spans="1:1" ht="22.5">
+      <c r="G25" s="24"/>
+    </row>
+    <row r="26" spans="1:8" ht="40.5" customHeight="1">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" ht="22.5">
+    <row r="27" spans="1:8" ht="23.25" customHeight="1">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" ht="22.5">
+    <row r="28" spans="1:8" ht="23.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" ht="22.5">
+    <row r="29" spans="1:8" ht="23.25" customHeight="1">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" ht="22.5">
+    <row r="30" spans="1:8" ht="23.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" ht="22.5">
+    <row r="31" spans="1:8" ht="23.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" ht="22.5">
+    <row r="32" spans="1:8" ht="23.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" ht="22.5">
+    <row r="33" spans="1:1" ht="23.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" ht="22.5">
+    <row r="34" spans="1:1" ht="23.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" ht="22.5">
+    <row r="35" spans="1:1" ht="23.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" ht="22.5">
+    <row r="36" spans="1:1" ht="23.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" ht="22.5">
+    <row r="37" spans="1:1" ht="23.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" ht="22.5">
+    <row r="38" spans="1:1" ht="23.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" ht="22.5">
+    <row r="39" spans="1:1" ht="23.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" ht="22.5">
+    <row r="40" spans="1:1" ht="23.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" ht="22.5">
+    <row r="41" spans="1:1" ht="23.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" ht="22.5">
+    <row r="42" spans="1:1" ht="23.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" ht="22.5">
+    <row r="43" spans="1:1" ht="23.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" ht="22.5">
+    <row r="44" spans="1:1" ht="23.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" ht="22.5">
+    <row r="45" spans="1:1" ht="23.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" ht="22.5">
+    <row r="46" spans="1:1" ht="23.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" ht="22.5">
+    <row r="47" spans="1:1" ht="23.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" ht="22.5">
+    <row r="48" spans="1:1" ht="23.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" ht="22.5">
+    <row r="49" spans="1:1" ht="23.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" ht="22.5">
+    <row r="50" spans="1:1" ht="23.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" ht="22.5">
+    <row r="51" spans="1:1" ht="23.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" ht="22.5">
+    <row r="52" spans="1:1" ht="23.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" ht="22.5">
+    <row r="53" spans="1:1" ht="23.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" ht="22.5">
+    <row r="54" spans="1:1" ht="23.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" ht="22.5">
+    <row r="55" spans="1:1" ht="23.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" ht="22.5">
+    <row r="56" spans="1:1" ht="23.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" ht="22.5">
+    <row r="57" spans="1:1" ht="23.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" ht="22.5">
+    <row r="58" spans="1:1" ht="23.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" ht="22.5">
+    <row r="59" spans="1:1" ht="23.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" ht="22.5">
+    <row r="60" spans="1:1" ht="23.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" ht="22.5">
+    <row r="61" spans="1:1" ht="23.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" ht="22.5">
+    <row r="62" spans="1:1" ht="23.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" ht="22.5">
+    <row r="63" spans="1:1" ht="23.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" ht="22.5">
+    <row r="64" spans="1:1" ht="23.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" ht="22.5">
+    <row r="65" spans="1:1" ht="23.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" ht="22.5">
+    <row r="66" spans="1:1" ht="23.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" ht="22.5">
+    <row r="67" spans="1:1" ht="23.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" ht="22.5">
+    <row r="68" spans="1:1" ht="23.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" ht="22.5">
+    <row r="69" spans="1:1" ht="23.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" ht="22.5">
+    <row r="70" spans="1:1" ht="23.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" ht="22.5">
+    <row r="71" spans="1:1" ht="23.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" ht="22.5">
+    <row r="72" spans="1:1" ht="23.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" ht="22.5">
+    <row r="73" spans="1:1" ht="23.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" ht="22.5">
+    <row r="74" spans="1:1" ht="23.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" ht="22.5">
+    <row r="75" spans="1:1" ht="23.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" ht="22.5">
+    <row r="76" spans="1:1" ht="23.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" ht="22.5">
+    <row r="77" spans="1:1" ht="23.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" ht="22.5">
+    <row r="78" spans="1:1" ht="23.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" ht="22.5">
+    <row r="79" spans="1:1" ht="23.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" ht="22.5">
+    <row r="80" spans="1:1" ht="23.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" ht="22.5">
+    <row r="81" spans="1:1" ht="23.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" ht="22.5">
+    <row r="82" spans="1:1" ht="23.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" ht="22.5">
+    <row r="83" spans="1:1" ht="23.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" ht="22.5">
+    <row r="84" spans="1:1" ht="23.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" ht="22.5">
+    <row r="85" spans="1:1" ht="23.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" ht="22.5">
+    <row r="86" spans="1:1" ht="23.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" ht="22.5">
+    <row r="87" spans="1:1" ht="23.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" ht="22.5">
+    <row r="88" spans="1:1" ht="23.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" ht="22.5">
+    <row r="89" spans="1:1" ht="23.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" ht="22.5">
+    <row r="90" spans="1:1" ht="23.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" ht="22.5">
+    <row r="91" spans="1:1" ht="23.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" ht="22.5">
+    <row r="92" spans="1:1" ht="23.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" ht="22.5">
+    <row r="93" spans="1:1" ht="23.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" ht="22.5">
+    <row r="94" spans="1:1" ht="23.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" ht="22.5">
+    <row r="95" spans="1:1" ht="23.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" ht="22.5">
+    <row r="96" spans="1:1" ht="23.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" ht="22.5">
+    <row r="97" spans="1:1" ht="23.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" ht="22.5">
+    <row r="98" spans="1:1" ht="23.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" ht="22.5">
+    <row r="99" spans="1:1" ht="23.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" ht="22.5">
+    <row r="100" spans="1:1" ht="23.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" ht="22.5">
+    <row r="101" spans="1:1" ht="23.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" ht="22.5">
+    <row r="102" spans="1:1" ht="23.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" ht="22.5">
+    <row r="103" spans="1:1" ht="23.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" ht="22.5">
+    <row r="104" spans="1:1" ht="23.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" ht="22.5">
+    <row r="105" spans="1:1" ht="23.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" ht="22.5">
+    <row r="106" spans="1:1" ht="23.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" ht="22.5">
+    <row r="107" spans="1:1" ht="23.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" ht="22.5">
+    <row r="108" spans="1:1" ht="23.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" ht="22.5">
+    <row r="109" spans="1:1" ht="23.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" ht="22.5">
+    <row r="110" spans="1:1" ht="23.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" ht="22.5">
+    <row r="111" spans="1:1" ht="23.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" ht="22.5">
+    <row r="112" spans="1:1" ht="23.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" ht="22.5">
+    <row r="113" spans="1:1" ht="23.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" ht="22.5">
+    <row r="114" spans="1:1" ht="23.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" ht="22.5">
+    <row r="115" spans="1:1" ht="23.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" ht="22.5">
+    <row r="116" spans="1:1" ht="23.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" ht="22.5">
+    <row r="117" spans="1:1" ht="23.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" ht="22.5">
+    <row r="118" spans="1:1" ht="23.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" ht="22.5">
+    <row r="119" spans="1:1" ht="23.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" ht="22.5">
+    <row r="120" spans="1:1" ht="23.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" ht="22.5">
+    <row r="121" spans="1:1" ht="23.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" ht="22.5">
+    <row r="122" spans="1:1" ht="23.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" ht="22.5">
+    <row r="123" spans="1:1" ht="23.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" ht="22.5">
+    <row r="124" spans="1:1" ht="23.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" ht="22.5">
+    <row r="125" spans="1:1" ht="23.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" ht="22.5">
+    <row r="126" spans="1:1" ht="23.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" ht="22.5">
+    <row r="127" spans="1:1" ht="23.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" ht="22.5">
+    <row r="128" spans="1:1" ht="23.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" ht="22.5">
+    <row r="129" spans="1:1" ht="23.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" ht="22.5">
+    <row r="130" spans="1:1" ht="23.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" ht="22.5">
+    <row r="131" spans="1:1" ht="23.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" ht="22.5">
+    <row r="132" spans="1:1" ht="23.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" ht="22.5">
+    <row r="133" spans="1:1" ht="23.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" ht="22.5">
+    <row r="134" spans="1:1" ht="23.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" ht="22.5">
+    <row r="135" spans="1:1" ht="23.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" ht="22.5">
+    <row r="136" spans="1:1" ht="23.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" ht="22.5">
+    <row r="137" spans="1:1" ht="23.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" ht="22.5">
+    <row r="138" spans="1:1" ht="23.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" ht="22.5">
+    <row r="139" spans="1:1" ht="23.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" ht="22.5">
+    <row r="140" spans="1:1" ht="23.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" ht="22.5">
+    <row r="141" spans="1:1" ht="23.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" ht="22.5">
+    <row r="142" spans="1:1" ht="23.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" ht="22.5">
+    <row r="143" spans="1:1" ht="23.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" ht="22.5">
+    <row r="144" spans="1:1" ht="23.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" ht="22.5">
+    <row r="145" spans="1:1" ht="23.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" ht="22.5">
+    <row r="146" spans="1:1" ht="23.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" ht="22.5">
+    <row r="147" spans="1:1" ht="23.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" ht="22.5">
+    <row r="148" spans="1:1" ht="23.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" ht="22.5">
+    <row r="149" spans="1:1" ht="23.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" ht="22.5">
+    <row r="150" spans="1:1" ht="23.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" ht="22.5">
+    <row r="151" spans="1:1" ht="23.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" ht="22.5">
+    <row r="152" spans="1:1" ht="23.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" ht="22.5">
+    <row r="153" spans="1:1" ht="23.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" ht="22.5">
+    <row r="154" spans="1:1" ht="23.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" ht="22.5">
+    <row r="155" spans="1:1" ht="23.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" ht="22.5">
+    <row r="156" spans="1:1" ht="23.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" ht="22.5">
+    <row r="157" spans="1:1" ht="23.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" ht="22.5">
+    <row r="158" spans="1:1" ht="23.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" ht="22.5">
+    <row r="159" spans="1:1" ht="23.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" ht="22.5">
+    <row r="160" spans="1:1" ht="23.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" ht="22.5">
+    <row r="161" spans="1:1" ht="23.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" ht="22.5">
+    <row r="162" spans="1:1" ht="23.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" ht="22.5">
+    <row r="163" spans="1:1" ht="23.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" ht="22.5">
+    <row r="164" spans="1:1" ht="23.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" ht="22.5">
+    <row r="165" spans="1:1" ht="23.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" ht="22.5">
+    <row r="166" spans="1:1" ht="23.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" ht="22.5">
+    <row r="167" spans="1:1" ht="23.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" ht="22.5">
+    <row r="168" spans="1:1" ht="23.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" ht="22.5">
+    <row r="169" spans="1:1" ht="23.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" ht="22.5">
+    <row r="170" spans="1:1" ht="23.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" ht="22.5">
+    <row r="171" spans="1:1" ht="23.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" ht="22.5">
+    <row r="172" spans="1:1" ht="23.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" ht="22.5">
+    <row r="173" spans="1:1" ht="23.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" ht="22.5">
+    <row r="174" spans="1:1" ht="23.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" ht="22.5">
+    <row r="175" spans="1:1" ht="23.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" ht="22.5">
+    <row r="176" spans="1:1" ht="23.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" ht="22.5">
+    <row r="177" spans="1:1" ht="23.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" ht="22.5">
+    <row r="178" spans="1:1" ht="23.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" ht="22.5">
+    <row r="179" spans="1:1" ht="23.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" ht="22.5">
+    <row r="180" spans="1:1" ht="23.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" ht="22.5">
+    <row r="181" spans="1:1" ht="23.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" ht="22.5">
+    <row r="182" spans="1:1" ht="23.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" ht="22.5">
-      <c r="A183" s="5"/>
-    </row>
-    <row r="184" spans="1:1" ht="22.5">
-      <c r="A184" s="5"/>
-    </row>
-    <row r="185" spans="1:1" ht="22.5">
-      <c r="A185" s="5"/>
-    </row>
-    <row r="186" spans="1:1" ht="22.5">
-      <c r="A186" s="5"/>
-    </row>
   </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="E7:E15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="D16:D20"/>
+    <mergeCell ref="E16:E20"/>
+    <mergeCell ref="C16:C20"/>
+    <mergeCell ref="B7:B15"/>
+    <mergeCell ref="A7:A15"/>
+    <mergeCell ref="C7:C15"/>
+    <mergeCell ref="D7:D15"/>
+    <mergeCell ref="F7:F15"/>
+    <mergeCell ref="G7:G15"/>
+    <mergeCell ref="H7:H15"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="H16:H20"/>
+  </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="10" orientation="landscape" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId1"/>
   <extLst>
@@ -1652,7 +2052,7 @@
           <x14:formula1>
             <xm:f>catagories!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>B1:B1048576</xm:sqref>
+          <xm:sqref>B1:B7 B16 B21:B1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1663,25 +2063,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="1"/>
-    <col min="2" max="2" width="41.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="43.90625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="38.08984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="43.6328125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.90625" style="1"/>
+    <col min="1" max="1" width="10.85546875" style="1"/>
+    <col min="2" max="2" width="41.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="42.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="38.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="43.5703125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="2:2">
@@ -1691,22 +2091,22 @@
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1716,21 +2116,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010006807B066C556C4DA1F97EE96CC1104B" ma:contentTypeVersion="13" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="cfb987611df5cdae7f7a5067c3395bc7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c2ee6f6c-285d-4b95-ace0-9682ebe56039" xmlns:ns3="012b183d-1ada-4ff6-b855-98c4d59bda2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2586826dc5d0b05e832f2b79fc23a" ns2:_="" ns3:_="">
     <xsd:import namespace="c2ee6f6c-285d-4b95-ace0-9682ebe56039"/>
@@ -1953,32 +2338,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C795275D-8D89-4504-820D-42600FA03DDE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9479F6B-BC70-40D1-9DD0-21D0DC99C2BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="012b183d-1ada-4ff6-b855-98c4d59bda2b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c2ee6f6c-285d-4b95-ace0-9682ebe56039"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E55E6835-5439-4B85-9C34-8A416D678E4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1995,4 +2370,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9479F6B-BC70-40D1-9DD0-21D0DC99C2BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="012b183d-1ada-4ff6-b855-98c4d59bda2b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c2ee6f6c-285d-4b95-ace0-9682ebe56039"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C795275D-8D89-4504-820D-42600FA03DDE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>